--- a/Assets/0_Adventure/Deploy/스테이지.xlsx
+++ b/Assets/0_Adventure/Deploy/스테이지.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user\Desktop\Game Porject\Adventure\Assets\0_Adventure\Deploy\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9DE2A218-6980-409A-8C59-7B7A7E0D7F87}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9F34E2B6-8810-4214-9BAA-F64BC9EA30F0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11" uniqueCount="11">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6" uniqueCount="6">
   <si>
     <t>스테이지</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -48,26 +48,6 @@
   </si>
   <si>
     <t>몬스터 속도</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>돌 공장 X 2, 도로 X 4, 새총 X 2</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>궁수 X3, 화살공장 X 3, 도로 X 4</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>총알 공장 X 3, 도로 X 15, 총 X1</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>공장 버프 X3, 타워버프 X2, 총 X3</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>지을 수 있는 건물(기본으로 1을 지을 수 있고, 깨면 건물이 추가됨)</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -427,9 +407,6 @@
       <c r="F1" t="s">
         <v>4</v>
       </c>
-      <c r="G1" t="s">
-        <v>10</v>
-      </c>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A2">
@@ -450,9 +427,6 @@
       <c r="F2">
         <v>1200</v>
       </c>
-      <c r="G2" t="s">
-        <v>6</v>
-      </c>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A3">
@@ -473,9 +447,6 @@
       <c r="F3">
         <v>3000</v>
       </c>
-      <c r="G3" t="s">
-        <v>7</v>
-      </c>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A4">
@@ -496,9 +467,6 @@
       <c r="F4">
         <v>5000</v>
       </c>
-      <c r="G4" t="s">
-        <v>8</v>
-      </c>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A5">
@@ -518,9 +486,6 @@
       </c>
       <c r="F5">
         <v>0</v>
-      </c>
-      <c r="G5" t="s">
-        <v>9</v>
       </c>
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.3">

--- a/Assets/0_Adventure/Deploy/스테이지.xlsx
+++ b/Assets/0_Adventure/Deploy/스테이지.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user\Desktop\Game Porject\Adventure\Assets\0_Adventure\Deploy\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9F34E2B6-8810-4214-9BAA-F64BC9EA30F0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B6F30505-A6CB-4A6C-8383-CAD53F3D5887}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -424,9 +424,6 @@
       <c r="E2">
         <v>3</v>
       </c>
-      <c r="F2">
-        <v>1200</v>
-      </c>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A3">
@@ -444,9 +441,6 @@
       <c r="E3">
         <v>5</v>
       </c>
-      <c r="F3">
-        <v>3000</v>
-      </c>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A4">
@@ -464,9 +458,6 @@
       <c r="E4">
         <v>7</v>
       </c>
-      <c r="F4">
-        <v>5000</v>
-      </c>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A5">
@@ -482,10 +473,58 @@
         <v>5</v>
       </c>
       <c r="E5">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A6">
+        <v>5</v>
+      </c>
+      <c r="B6">
+        <v>500</v>
+      </c>
+      <c r="C6">
+        <v>0.7</v>
+      </c>
+      <c r="D6">
+        <v>5</v>
+      </c>
+      <c r="E6">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A7">
+        <v>6</v>
+      </c>
+      <c r="B7">
+        <v>800</v>
+      </c>
+      <c r="C7">
+        <v>0.7</v>
+      </c>
+      <c r="D7">
+        <v>5</v>
+      </c>
+      <c r="E7">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A8">
+        <v>7</v>
+      </c>
+      <c r="B8">
+        <v>1000</v>
+      </c>
+      <c r="C8">
+        <v>0.7</v>
+      </c>
+      <c r="D8">
+        <v>5</v>
+      </c>
+      <c r="E8">
         <v>10</v>
-      </c>
-      <c r="F5">
-        <v>0</v>
       </c>
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.3">
